--- a/toy_models/farm_toy_v5_full_calendar.xlsx
+++ b/toy_models/farm_toy_v5_full_calendar.xlsx
@@ -567,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:A136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -693,14 +693,14 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">     v5 without the minimum-acreage rule     $2,347,941   (41 plantings)</t>
+          <t xml:space="preserve">     v5 without the minimum-acreage rule     $2,387,990   (42 plantings)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     v5 as it ships                          $2,345,898   (30 plantings)</t>
+          <t xml:space="preserve">     v5 as it ships                          $2,384,231   (33 plantings)</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>$2,044 back and drops the plan from 41 plantings to 30, because the</t>
+          <t>$3,759 back and drops the plan from 42 plantings to 33, because the</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>30 plantings out of 68, staggered across the season rather than a few big</t>
+          <t>33 plantings out of 68, staggered across the season rather than a few big</t>
         </is>
       </c>
     </row>
@@ -941,14 +941,14 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     PROFIT   $2,345,898      = revenue $2,519,404 - growing cost $173,506</t>
+          <t xml:space="preserve">     PROFIT   $2,384,231      = revenue $2,558,846 - growing cost $174,616</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     30 of 68 plantings used</t>
+          <t xml:space="preserve">     33 of 68 plantings used</t>
         </is>
       </c>
     </row>
@@ -982,45 +982,45 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>TWO THINGS TO TRY</t>
+          <t>WHAT SELL-THROUGH IS, AND WHY IT SHIPS AT 1.00</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Every 'Sell-through' in section 3 is 1.00, matching the app since 30 Aug. The 85% it used to</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 1 — drop the minimum acreage.  Set every 'Min acres if planted' in the crop</t>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>carry had no source, and it was being charged on channels where a purchase order exists and</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   table to 0 and re-solve.</t>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>nothing goes unsold. So the market-loss and returned-to-store rows all read ZERO right now.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Expect $2,347,941 and 41 plantings. The extra profit is real but the plan is</t>
+          <t>That is correct, not broken.</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   not: it plants fractions of an acre no one would drive a tractor out for. This is what</t>
-        </is>
-      </c>
+      <c r="A72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the binaries are FOR, and it is why the app carries them.</t>
+          <t>The narrow definition it now carries:</t>
         </is>
       </c>
     </row>
@@ -1030,118 +1030,110 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>EXPERIMENT 2 — take away the cooler.  Set the cold store to 40 m3 and re-solve.</t>
+          <t xml:space="preserve">     Of what you TAKE TO MARKET, the share that converts to cash — display attrition at a</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Watch WHICH WEEKS it abandons, not just which crop. With a full calendar it can retreat</t>
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     stall, samples, transit damage, a rejected load.</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   to a planting pattern that keeps the cooler under its ceiling — an answer v4 could not</t>
-        </is>
-      </c>
+      <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">   even represent.</t>
+          <t>NOT grade-out at harvest (that is pack-out, above the store). NOT spoilage in the store (that</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>is shrink). And NOT demand uncertainty — which is the one worth understanding, because it is</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>WHAT v5 STILL DOES NOT CARRY</t>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>why the old wording could not be right:</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY: no labour, water, packaging, storage, overhead.</t>
-        </is>
-      </c>
+      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Profit is therefore far too high. The cash layer is next.</t>
+          <t xml:space="preserve">     The demand ceiling is HARD. At a 6,000 lb cap and 0.85, selling 6,000 means bringing</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
+          <t xml:space="preserve">     7,059 and losing 1,059 — every week, including the best Saturday of the year, because</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Shelf life is not enforced here (it was a warning row in v3/v4; with a full calendar the</t>
+          <t xml:space="preserve">     the model will never let you sell 6,001. That is the whole downside of bringing extra</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">    warning became noise, so it is out until it can be a real constraint).</t>
+          <t xml:space="preserve">     with none of the upside. It is not a model of uncertainty; it is a one-sided penalty.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - No water, labour, diversity or throughput limits.</t>
-        </is>
-      </c>
+      <c r="A86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Three crops, not seven.</t>
+          <t>So what it CAN mean is a display requirement: a picked-over stall sells less than a full one,</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>so moving 6,000 lb needs more than 6,000 lb on the table. Deterministic, and an input</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>!! THE SCALE WARNING</t>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>requirement like seed. Real demand variance is a different problem (newsvendor) needing</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>An optimizer's answer is far more scale-sensitive than a calculator's: which constraint binds,</t>
+          <t>machinery neither this sheet nor the app has yet.</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>and therefore which crop and which WEEK wins, can invert between 3 crops and 7. This teaches</t>
-        </is>
-      </c>
+      <c r="A91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>the machinery. It is not advice about your farm.</t>
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>THREE THINGS TO TRY</t>
         </is>
       </c>
     </row>
@@ -1149,49 +1141,281 @@
       <c r="A93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>HAS THIS SHEET BEEN CHECKED?</t>
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 1 — switch sell-through on, and watch the crop decide what happens.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Yes. Crop data, the calendar and the demand caps are read from the app. The formulas are</t>
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   In section 3 set Spinach / {CH1} sell-through to 0.85, and Garlic / {CH1} to 0.85 too.</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>calculated by an engine and compared cell by cell against an independent model under three</t>
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Re-solve.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>configurations. Every input is perturbed to prove it propagates. No number is frozen. And the</t>
+          <t xml:space="preserve">   Both now offer more than they sell. But look at the two 'market loss' rows: Spinach's is</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>same MILP is solved with scipy.milp, its answer written into the decision cells, and the</t>
+          <t xml:space="preserve">   positive and Garlic's is ZERO, because garlic's 'Returns to store' is 1.00 — unsold garlic</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>sheet's own PROFIT cell must reproduce the optimum exactly.</t>
+          <t xml:space="preserve">   comes home and sells later, so the loss is a DELAY, not a loss.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   That is the grower's ruling in two cells: the same sell-through means different things on</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   different crops, which is why it belongs on the crop x channel row and not on either one</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   alone. Now set Garlic's 'Returns to store' to 0.00 and re-solve: the delay becomes a loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   and the plan changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 2 — drop the minimum acreage.  Set every 'Min acres if planted' in the crop</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   table to 0 and re-solve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Expect $2,387,990 and 42 plantings. The extra profit is real but the plan is</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   not: it plants fractions of an acre no one would drive a tractor out for. This is what</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the binaries are FOR, and it is why the app carries them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 3 — take away the cooler.  Set the cold store to 40 m3 and re-solve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Watch WHICH WEEKS it abandons, not just which crop. With a full calendar it can retreat</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   to a planting pattern that keeps the cooler under its ceiling — an answer v4 could not</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   even represent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>WHAT v5 STILL DOES NOT CARRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY: no labour, water, packaging, storage, overhead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Profit is therefore far too high. The cash layer is next.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Shelf life IS enforced now (a real constraint since you found it dead). Shrink is wired</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    too, but defaults to 0%, so it stays invisible until you set it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - No water, labour, diversity or throughput limits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Three crops, not seven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>!! THE SCALE WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>An optimizer's answer is far more scale-sensitive than a calculator's: which constraint binds,</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>and therefore which crop and which WEEK wins, can invert between 3 crops and 7. This teaches</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>the machinery. It is not advice about your farm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>HAS THIS SHEET BEEN CHECKED?</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Yes. Crop data, the calendar and the demand caps are read from the app. The formulas are</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>calculated by an engine and compared cell by cell against an independent model under three</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>configurations. Every input is perturbed to prove it propagates. No number is frozen. And the</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>same MILP is solved with scipy.milp, its answer written into the decision cells, and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>sheet's own PROFIT cell must reproduce the optimum exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
         <is>
           <t xml:space="preserve">     Run it yourself:   .venv/bin/python toy_models/verify_toy_v5.py</t>
         </is>
@@ -1578,7 +1802,7 @@
         <v>48</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H18" s="9" t="n">
         <v>0</v>
@@ -1648,7 +1872,7 @@
         <v>50</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H20" s="9" t="n">
         <v>0</v>
@@ -1718,7 +1942,7 @@
         <v>35</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="H22" s="9" t="n">
         <v>1</v>

--- a/toy_models/farm_toy_v5_full_calendar.xlsx
+++ b/toy_models/farm_toy_v5_full_calendar.xlsx
@@ -137,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +188,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -15827,212 +15828,212 @@
           <t>lb</t>
         </is>
       </c>
-      <c r="E142" s="40">
+      <c r="E142" s="44">
         <f>IF($C$21="Annual",$D$21-0,IF(AND(1&gt;=$E$21,1&lt;=$F$21),$D$21,0))</f>
         <v/>
       </c>
-      <c r="F142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:E144),IF(AND(2&gt;=$E$21,2&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="G142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:F144),IF(AND(3&gt;=$E$21,3&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="H142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:G144),IF(AND(4&gt;=$E$21,4&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="I142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:H144),IF(AND(5&gt;=$E$21,5&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="J142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:I144),IF(AND(6&gt;=$E$21,6&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="K142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:J144),IF(AND(7&gt;=$E$21,7&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="L142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:K144),IF(AND(8&gt;=$E$21,8&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="M142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:L144),IF(AND(9&gt;=$E$21,9&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="N142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:M144),IF(AND(10&gt;=$E$21,10&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="O142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:N144),IF(AND(11&gt;=$E$21,11&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="P142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:O144),IF(AND(12&gt;=$E$21,12&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="Q142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:P144),IF(AND(13&gt;=$E$21,13&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="R142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:Q144),IF(AND(14&gt;=$E$21,14&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="S142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:R144),IF(AND(15&gt;=$E$21,15&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="T142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:S144),IF(AND(16&gt;=$E$21,16&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="U142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:T144),IF(AND(17&gt;=$E$21,17&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="V142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:U144),IF(AND(18&gt;=$E$21,18&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="W142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:V144),IF(AND(19&gt;=$E$21,19&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="X142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:W144),IF(AND(20&gt;=$E$21,20&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="Y142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:X144),IF(AND(21&gt;=$E$21,21&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="Z142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:Y144),IF(AND(22&gt;=$E$21,22&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AA142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:Z144),IF(AND(23&gt;=$E$21,23&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AB142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AA144),IF(AND(24&gt;=$E$21,24&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AC142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AB144),IF(AND(25&gt;=$E$21,25&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AD142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AC144),IF(AND(26&gt;=$E$21,26&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AE142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AD144),IF(AND(27&gt;=$E$21,27&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AF142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AE144),IF(AND(28&gt;=$E$21,28&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AG142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AF144),IF(AND(29&gt;=$E$21,29&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AH142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AG144),IF(AND(30&gt;=$E$21,30&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AI142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AH144),IF(AND(31&gt;=$E$21,31&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AJ142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AI144),IF(AND(32&gt;=$E$21,32&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AK142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AJ144),IF(AND(33&gt;=$E$21,33&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AL142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AK144),IF(AND(34&gt;=$E$21,34&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AM142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AL144),IF(AND(35&gt;=$E$21,35&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AN142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AM144),IF(AND(36&gt;=$E$21,36&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AO142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AN144),IF(AND(37&gt;=$E$21,37&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AP142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AO144),IF(AND(38&gt;=$E$21,38&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AQ142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AP144),IF(AND(39&gt;=$E$21,39&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AR142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AQ144),IF(AND(40&gt;=$E$21,40&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AS142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AR144),IF(AND(41&gt;=$E$21,41&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AT142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AS144),IF(AND(42&gt;=$E$21,42&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AU142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AT144),IF(AND(43&gt;=$E$21,43&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AV142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AU144),IF(AND(44&gt;=$E$21,44&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AW142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AV144),IF(AND(45&gt;=$E$21,45&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AX142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AW144),IF(AND(46&gt;=$E$21,46&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AY142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AX144),IF(AND(47&gt;=$E$21,47&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="AZ142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AY144),IF(AND(48&gt;=$E$21,48&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="BA142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:AZ144),IF(AND(49&gt;=$E$21,49&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="BB142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:BA144),IF(AND(50&gt;=$E$21,50&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="BC142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:BB144),IF(AND(51&gt;=$E$21,51&lt;=$F$21),$D$21,0))</f>
-        <v/>
-      </c>
-      <c r="BD142" s="40">
-        <f>IF($C$21="Annual",$D$21-SUM(E144:BC144),IF(AND(52&gt;=$E$21,52&lt;=$F$21),$D$21,0))</f>
+      <c r="F142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:E146),IF(AND(2&gt;=$E$21,2&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="G142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:F146),IF(AND(3&gt;=$E$21,3&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="H142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:G146),IF(AND(4&gt;=$E$21,4&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="I142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:H146),IF(AND(5&gt;=$E$21,5&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="J142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:I146),IF(AND(6&gt;=$E$21,6&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="K142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:J146),IF(AND(7&gt;=$E$21,7&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="L142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:K146),IF(AND(8&gt;=$E$21,8&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="M142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:L146),IF(AND(9&gt;=$E$21,9&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="N142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:M146),IF(AND(10&gt;=$E$21,10&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="O142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:N146),IF(AND(11&gt;=$E$21,11&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="P142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:O146),IF(AND(12&gt;=$E$21,12&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="Q142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:P146),IF(AND(13&gt;=$E$21,13&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="R142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:Q146),IF(AND(14&gt;=$E$21,14&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="S142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:R146),IF(AND(15&gt;=$E$21,15&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="T142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:S146),IF(AND(16&gt;=$E$21,16&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="U142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:T146),IF(AND(17&gt;=$E$21,17&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="V142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:U146),IF(AND(18&gt;=$E$21,18&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="W142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:V146),IF(AND(19&gt;=$E$21,19&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="X142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:W146),IF(AND(20&gt;=$E$21,20&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="Y142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:X146),IF(AND(21&gt;=$E$21,21&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="Z142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:Y146),IF(AND(22&gt;=$E$21,22&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AA142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:Z146),IF(AND(23&gt;=$E$21,23&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AB142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AA146),IF(AND(24&gt;=$E$21,24&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AC142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AB146),IF(AND(25&gt;=$E$21,25&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AD142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AC146),IF(AND(26&gt;=$E$21,26&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AE142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AD146),IF(AND(27&gt;=$E$21,27&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AF142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AE146),IF(AND(28&gt;=$E$21,28&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AG142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AF146),IF(AND(29&gt;=$E$21,29&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AH142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AG146),IF(AND(30&gt;=$E$21,30&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AI142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AH146),IF(AND(31&gt;=$E$21,31&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AJ142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AI146),IF(AND(32&gt;=$E$21,32&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AK142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AJ146),IF(AND(33&gt;=$E$21,33&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AL142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AK146),IF(AND(34&gt;=$E$21,34&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AM142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AL146),IF(AND(35&gt;=$E$21,35&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AN142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AM146),IF(AND(36&gt;=$E$21,36&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AO142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AN146),IF(AND(37&gt;=$E$21,37&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AP142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AO146),IF(AND(38&gt;=$E$21,38&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AQ142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AP146),IF(AND(39&gt;=$E$21,39&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AR142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AQ146),IF(AND(40&gt;=$E$21,40&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AS142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AR146),IF(AND(41&gt;=$E$21,41&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AT142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AS146),IF(AND(42&gt;=$E$21,42&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AU142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AT146),IF(AND(43&gt;=$E$21,43&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AV142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AU146),IF(AND(44&gt;=$E$21,44&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AW142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AV146),IF(AND(45&gt;=$E$21,45&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AX142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AW146),IF(AND(46&gt;=$E$21,46&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AY142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AX146),IF(AND(47&gt;=$E$21,47&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="AZ142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AY146),IF(AND(48&gt;=$E$21,48&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="BA142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:AZ146),IF(AND(49&gt;=$E$21,49&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="BB142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:BA146),IF(AND(50&gt;=$E$21,50&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="BC142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:BB146),IF(AND(51&gt;=$E$21,51&lt;=$F$21),$D$21,0))</f>
+        <v/>
+      </c>
+      <c r="BD142" s="44">
+        <f>IF($C$21="Annual",$D$21-SUM(E146:BC146),IF(AND(52&gt;=$E$21,52&lt;=$F$21),$D$21,0))</f>
         <v/>
       </c>
     </row>
@@ -17785,7 +17786,7 @@
           <t>GARLIC  —  ambient store</t>
         </is>
       </c>
-      <c r="B157" s="44" t="inlineStr"/>
+      <c r="B157" s="45" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="19" t="inlineStr">
@@ -21838,211 +21839,211 @@
           <t>m3</t>
         </is>
       </c>
-      <c r="E180" s="45">
+      <c r="E180" s="46">
         <f>(E160+E159)*$D$13</f>
         <v/>
       </c>
-      <c r="F180" s="45">
+      <c r="F180" s="46">
         <f>(F160+F159)*$D$13</f>
         <v/>
       </c>
-      <c r="G180" s="45">
+      <c r="G180" s="46">
         <f>(G160+G159)*$D$13</f>
         <v/>
       </c>
-      <c r="H180" s="45">
+      <c r="H180" s="46">
         <f>(H160+H159)*$D$13</f>
         <v/>
       </c>
-      <c r="I180" s="45">
+      <c r="I180" s="46">
         <f>(I160+I159)*$D$13</f>
         <v/>
       </c>
-      <c r="J180" s="45">
+      <c r="J180" s="46">
         <f>(J160+J159)*$D$13</f>
         <v/>
       </c>
-      <c r="K180" s="45">
+      <c r="K180" s="46">
         <f>(K160+K159)*$D$13</f>
         <v/>
       </c>
-      <c r="L180" s="45">
+      <c r="L180" s="46">
         <f>(L160+L159)*$D$13</f>
         <v/>
       </c>
-      <c r="M180" s="45">
+      <c r="M180" s="46">
         <f>(M160+M159)*$D$13</f>
         <v/>
       </c>
-      <c r="N180" s="45">
+      <c r="N180" s="46">
         <f>(N160+N159)*$D$13</f>
         <v/>
       </c>
-      <c r="O180" s="45">
+      <c r="O180" s="46">
         <f>(O160+O159)*$D$13</f>
         <v/>
       </c>
-      <c r="P180" s="45">
+      <c r="P180" s="46">
         <f>(P160+P159)*$D$13</f>
         <v/>
       </c>
-      <c r="Q180" s="45">
+      <c r="Q180" s="46">
         <f>(Q160+Q159)*$D$13</f>
         <v/>
       </c>
-      <c r="R180" s="45">
+      <c r="R180" s="46">
         <f>(R160+R159)*$D$13</f>
         <v/>
       </c>
-      <c r="S180" s="45">
+      <c r="S180" s="46">
         <f>(S160+S159)*$D$13</f>
         <v/>
       </c>
-      <c r="T180" s="45">
+      <c r="T180" s="46">
         <f>(T160+T159)*$D$13</f>
         <v/>
       </c>
-      <c r="U180" s="45">
+      <c r="U180" s="46">
         <f>(U160+U159)*$D$13</f>
         <v/>
       </c>
-      <c r="V180" s="45">
+      <c r="V180" s="46">
         <f>(V160+V159)*$D$13</f>
         <v/>
       </c>
-      <c r="W180" s="45">
+      <c r="W180" s="46">
         <f>(W160+W159)*$D$13</f>
         <v/>
       </c>
-      <c r="X180" s="45">
+      <c r="X180" s="46">
         <f>(X160+X159)*$D$13</f>
         <v/>
       </c>
-      <c r="Y180" s="45">
+      <c r="Y180" s="46">
         <f>(Y160+Y159)*$D$13</f>
         <v/>
       </c>
-      <c r="Z180" s="45">
+      <c r="Z180" s="46">
         <f>(Z160+Z159)*$D$13</f>
         <v/>
       </c>
-      <c r="AA180" s="45">
+      <c r="AA180" s="46">
         <f>(AA160+AA159)*$D$13</f>
         <v/>
       </c>
-      <c r="AB180" s="45">
+      <c r="AB180" s="46">
         <f>(AB160+AB159)*$D$13</f>
         <v/>
       </c>
-      <c r="AC180" s="45">
+      <c r="AC180" s="46">
         <f>(AC160+AC159)*$D$13</f>
         <v/>
       </c>
-      <c r="AD180" s="45">
+      <c r="AD180" s="46">
         <f>(AD160+AD159)*$D$13</f>
         <v/>
       </c>
-      <c r="AE180" s="45">
+      <c r="AE180" s="46">
         <f>(AE160+AE159)*$D$13</f>
         <v/>
       </c>
-      <c r="AF180" s="45">
+      <c r="AF180" s="46">
         <f>(AF160+AF159)*$D$13</f>
         <v/>
       </c>
-      <c r="AG180" s="45">
+      <c r="AG180" s="46">
         <f>(AG160+AG159)*$D$13</f>
         <v/>
       </c>
-      <c r="AH180" s="45">
+      <c r="AH180" s="46">
         <f>(AH160+AH159)*$D$13</f>
         <v/>
       </c>
-      <c r="AI180" s="45">
+      <c r="AI180" s="46">
         <f>(AI160+AI159)*$D$13</f>
         <v/>
       </c>
-      <c r="AJ180" s="45">
+      <c r="AJ180" s="46">
         <f>(AJ160+AJ159)*$D$13</f>
         <v/>
       </c>
-      <c r="AK180" s="45">
+      <c r="AK180" s="46">
         <f>(AK160+AK159)*$D$13</f>
         <v/>
       </c>
-      <c r="AL180" s="45">
+      <c r="AL180" s="46">
         <f>(AL160+AL159)*$D$13</f>
         <v/>
       </c>
-      <c r="AM180" s="45">
+      <c r="AM180" s="46">
         <f>(AM160+AM159)*$D$13</f>
         <v/>
       </c>
-      <c r="AN180" s="45">
+      <c r="AN180" s="46">
         <f>(AN160+AN159)*$D$13</f>
         <v/>
       </c>
-      <c r="AO180" s="45">
+      <c r="AO180" s="46">
         <f>(AO160+AO159)*$D$13</f>
         <v/>
       </c>
-      <c r="AP180" s="45">
+      <c r="AP180" s="46">
         <f>(AP160+AP159)*$D$13</f>
         <v/>
       </c>
-      <c r="AQ180" s="45">
+      <c r="AQ180" s="46">
         <f>(AQ160+AQ159)*$D$13</f>
         <v/>
       </c>
-      <c r="AR180" s="45">
+      <c r="AR180" s="46">
         <f>(AR160+AR159)*$D$13</f>
         <v/>
       </c>
-      <c r="AS180" s="45">
+      <c r="AS180" s="46">
         <f>(AS160+AS159)*$D$13</f>
         <v/>
       </c>
-      <c r="AT180" s="45">
+      <c r="AT180" s="46">
         <f>(AT160+AT159)*$D$13</f>
         <v/>
       </c>
-      <c r="AU180" s="45">
+      <c r="AU180" s="46">
         <f>(AU160+AU159)*$D$13</f>
         <v/>
       </c>
-      <c r="AV180" s="45">
+      <c r="AV180" s="46">
         <f>(AV160+AV159)*$D$13</f>
         <v/>
       </c>
-      <c r="AW180" s="45">
+      <c r="AW180" s="46">
         <f>(AW160+AW159)*$D$13</f>
         <v/>
       </c>
-      <c r="AX180" s="45">
+      <c r="AX180" s="46">
         <f>(AX160+AX159)*$D$13</f>
         <v/>
       </c>
-      <c r="AY180" s="45">
+      <c r="AY180" s="46">
         <f>(AY160+AY159)*$D$13</f>
         <v/>
       </c>
-      <c r="AZ180" s="45">
+      <c r="AZ180" s="46">
         <f>(AZ160+AZ159)*$D$13</f>
         <v/>
       </c>
-      <c r="BA180" s="45">
+      <c r="BA180" s="46">
         <f>(BA160+BA159)*$D$13</f>
         <v/>
       </c>
-      <c r="BB180" s="45">
+      <c r="BB180" s="46">
         <f>(BB160+BB159)*$D$13</f>
         <v/>
       </c>
-      <c r="BC180" s="45">
+      <c r="BC180" s="46">
         <f>(BC160+BC159)*$D$13</f>
         <v/>
       </c>
-      <c r="BD180" s="45">
+      <c r="BD180" s="46">
         <f>(BD160+BD159)*$D$13</f>
         <v/>
       </c>
@@ -22223,7 +22224,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="46" t="inlineStr">
+      <c r="A184" s="47" t="inlineStr">
         <is>
           <t>COLD STORE</t>
         </is>
@@ -23316,7 +23317,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="47" t="inlineStr">
+      <c r="A191" s="48" t="inlineStr">
         <is>
           <t>AMBIENT STORE</t>
         </is>
@@ -23326,211 +23327,211 @@
           <t>used</t>
         </is>
       </c>
-      <c r="E191" s="45">
+      <c r="E191" s="46">
         <f>E180</f>
         <v/>
       </c>
-      <c r="F191" s="45">
+      <c r="F191" s="46">
         <f>F180</f>
         <v/>
       </c>
-      <c r="G191" s="45">
+      <c r="G191" s="46">
         <f>G180</f>
         <v/>
       </c>
-      <c r="H191" s="45">
+      <c r="H191" s="46">
         <f>H180</f>
         <v/>
       </c>
-      <c r="I191" s="45">
+      <c r="I191" s="46">
         <f>I180</f>
         <v/>
       </c>
-      <c r="J191" s="45">
+      <c r="J191" s="46">
         <f>J180</f>
         <v/>
       </c>
-      <c r="K191" s="45">
+      <c r="K191" s="46">
         <f>K180</f>
         <v/>
       </c>
-      <c r="L191" s="45">
+      <c r="L191" s="46">
         <f>L180</f>
         <v/>
       </c>
-      <c r="M191" s="45">
+      <c r="M191" s="46">
         <f>M180</f>
         <v/>
       </c>
-      <c r="N191" s="45">
+      <c r="N191" s="46">
         <f>N180</f>
         <v/>
       </c>
-      <c r="O191" s="45">
+      <c r="O191" s="46">
         <f>O180</f>
         <v/>
       </c>
-      <c r="P191" s="45">
+      <c r="P191" s="46">
         <f>P180</f>
         <v/>
       </c>
-      <c r="Q191" s="45">
+      <c r="Q191" s="46">
         <f>Q180</f>
         <v/>
       </c>
-      <c r="R191" s="45">
+      <c r="R191" s="46">
         <f>R180</f>
         <v/>
       </c>
-      <c r="S191" s="45">
+      <c r="S191" s="46">
         <f>S180</f>
         <v/>
       </c>
-      <c r="T191" s="45">
+      <c r="T191" s="46">
         <f>T180</f>
         <v/>
       </c>
-      <c r="U191" s="45">
+      <c r="U191" s="46">
         <f>U180</f>
         <v/>
       </c>
-      <c r="V191" s="45">
+      <c r="V191" s="46">
         <f>V180</f>
         <v/>
       </c>
-      <c r="W191" s="45">
+      <c r="W191" s="46">
         <f>W180</f>
         <v/>
       </c>
-      <c r="X191" s="45">
+      <c r="X191" s="46">
         <f>X180</f>
         <v/>
       </c>
-      <c r="Y191" s="45">
+      <c r="Y191" s="46">
         <f>Y180</f>
         <v/>
       </c>
-      <c r="Z191" s="45">
+      <c r="Z191" s="46">
         <f>Z180</f>
         <v/>
       </c>
-      <c r="AA191" s="45">
+      <c r="AA191" s="46">
         <f>AA180</f>
         <v/>
       </c>
-      <c r="AB191" s="45">
+      <c r="AB191" s="46">
         <f>AB180</f>
         <v/>
       </c>
-      <c r="AC191" s="45">
+      <c r="AC191" s="46">
         <f>AC180</f>
         <v/>
       </c>
-      <c r="AD191" s="45">
+      <c r="AD191" s="46">
         <f>AD180</f>
         <v/>
       </c>
-      <c r="AE191" s="45">
+      <c r="AE191" s="46">
         <f>AE180</f>
         <v/>
       </c>
-      <c r="AF191" s="45">
+      <c r="AF191" s="46">
         <f>AF180</f>
         <v/>
       </c>
-      <c r="AG191" s="45">
+      <c r="AG191" s="46">
         <f>AG180</f>
         <v/>
       </c>
-      <c r="AH191" s="45">
+      <c r="AH191" s="46">
         <f>AH180</f>
         <v/>
       </c>
-      <c r="AI191" s="45">
+      <c r="AI191" s="46">
         <f>AI180</f>
         <v/>
       </c>
-      <c r="AJ191" s="45">
+      <c r="AJ191" s="46">
         <f>AJ180</f>
         <v/>
       </c>
-      <c r="AK191" s="45">
+      <c r="AK191" s="46">
         <f>AK180</f>
         <v/>
       </c>
-      <c r="AL191" s="45">
+      <c r="AL191" s="46">
         <f>AL180</f>
         <v/>
       </c>
-      <c r="AM191" s="45">
+      <c r="AM191" s="46">
         <f>AM180</f>
         <v/>
       </c>
-      <c r="AN191" s="45">
+      <c r="AN191" s="46">
         <f>AN180</f>
         <v/>
       </c>
-      <c r="AO191" s="45">
+      <c r="AO191" s="46">
         <f>AO180</f>
         <v/>
       </c>
-      <c r="AP191" s="45">
+      <c r="AP191" s="46">
         <f>AP180</f>
         <v/>
       </c>
-      <c r="AQ191" s="45">
+      <c r="AQ191" s="46">
         <f>AQ180</f>
         <v/>
       </c>
-      <c r="AR191" s="45">
+      <c r="AR191" s="46">
         <f>AR180</f>
         <v/>
       </c>
-      <c r="AS191" s="45">
+      <c r="AS191" s="46">
         <f>AS180</f>
         <v/>
       </c>
-      <c r="AT191" s="45">
+      <c r="AT191" s="46">
         <f>AT180</f>
         <v/>
       </c>
-      <c r="AU191" s="45">
+      <c r="AU191" s="46">
         <f>AU180</f>
         <v/>
       </c>
-      <c r="AV191" s="45">
+      <c r="AV191" s="46">
         <f>AV180</f>
         <v/>
       </c>
-      <c r="AW191" s="45">
+      <c r="AW191" s="46">
         <f>AW180</f>
         <v/>
       </c>
-      <c r="AX191" s="45">
+      <c r="AX191" s="46">
         <f>AX180</f>
         <v/>
       </c>
-      <c r="AY191" s="45">
+      <c r="AY191" s="46">
         <f>AY180</f>
         <v/>
       </c>
-      <c r="AZ191" s="45">
+      <c r="AZ191" s="46">
         <f>AZ180</f>
         <v/>
       </c>
-      <c r="BA191" s="45">
+      <c r="BA191" s="46">
         <f>BA180</f>
         <v/>
       </c>
-      <c r="BB191" s="45">
+      <c r="BB191" s="46">
         <f>BB180</f>
         <v/>
       </c>
-      <c r="BC191" s="45">
+      <c r="BC191" s="46">
         <f>BC180</f>
         <v/>
       </c>
-      <c r="BD191" s="45">
+      <c r="BD191" s="46">
         <f>BD180</f>
         <v/>
       </c>
@@ -24253,7 +24254,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B198" s="48">
+      <c r="B198" s="49">
         <f>SUM(E113:BD113)*$I$18+SUM(E119:BD119)*$I$19+SUM(E138:BD138)*$I$20+SUM(E146:BD146)*$I$21+SUM(E165:BD165)*$I$22+SUM(E171:BD171)*$I$23</f>
         <v/>
       </c>
@@ -24264,7 +24265,7 @@
           <t>Growing cost</t>
         </is>
       </c>
-      <c r="B199" s="48">
+      <c r="B199" s="49">
         <f>SUMPRODUCT($C$28:$C$95,($B$28:$B$95="Spinach")*$H$11+($B$28:$B$95="Kale")*$H$12+($B$28:$B$95="Garlic")*$H$13)</f>
         <v/>
       </c>
@@ -24280,7 +24281,7 @@
           <t>PROFIT  (the objective)</t>
         </is>
       </c>
-      <c r="B200" s="49">
+      <c r="B200" s="50">
         <f>B198-B199</f>
         <v/>
       </c>
@@ -24296,7 +24297,7 @@
           <t>Plantings chosen</t>
         </is>
       </c>
-      <c r="B201" s="50">
+      <c r="B201" s="51">
         <f>SUM($D$28:$D$95)</f>
         <v/>
       </c>

--- a/toy_models/farm_toy_v5_full_calendar.xlsx
+++ b/toy_models/farm_toy_v5_full_calendar.xlsx
@@ -13063,211 +13063,211 @@
         </is>
       </c>
       <c r="E126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;1-$F$11+2,$E$106:$BD$106,"&lt;="&amp;1)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=1-$F$11+2)*($E$106:$BD$106&lt;=1)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=1)*(1-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="F126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;2-$F$11+2,$E$106:$BD$106,"&lt;="&amp;2)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=2-$F$11+2)*($E$106:$BD$106&lt;=2)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=2)*(2-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="G126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;3-$F$11+2,$E$106:$BD$106,"&lt;="&amp;3)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=3-$F$11+2)*($E$106:$BD$106&lt;=3)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=3)*(3-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="H126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;4-$F$11+2,$E$106:$BD$106,"&lt;="&amp;4)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=4-$F$11+2)*($E$106:$BD$106&lt;=4)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=4)*(4-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="I126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;5-$F$11+2,$E$106:$BD$106,"&lt;="&amp;5)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=5-$F$11+2)*($E$106:$BD$106&lt;=5)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=5)*(5-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="J126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;6-$F$11+2,$E$106:$BD$106,"&lt;="&amp;6)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=6-$F$11+2)*($E$106:$BD$106&lt;=6)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=6)*(6-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="K126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;7-$F$11+2,$E$106:$BD$106,"&lt;="&amp;7)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=7-$F$11+2)*($E$106:$BD$106&lt;=7)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=7)*(7-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="L126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;8-$F$11+2,$E$106:$BD$106,"&lt;="&amp;8)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=8-$F$11+2)*($E$106:$BD$106&lt;=8)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=8)*(8-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="M126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;9-$F$11+2,$E$106:$BD$106,"&lt;="&amp;9)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=9-$F$11+2)*($E$106:$BD$106&lt;=9)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=9)*(9-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="N126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;10-$F$11+2,$E$106:$BD$106,"&lt;="&amp;10)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=10-$F$11+2)*($E$106:$BD$106&lt;=10)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=10)*(10-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="O126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;11-$F$11+2,$E$106:$BD$106,"&lt;="&amp;11)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=11-$F$11+2)*($E$106:$BD$106&lt;=11)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=11)*(11-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="P126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;12-$F$11+2,$E$106:$BD$106,"&lt;="&amp;12)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=12-$F$11+2)*($E$106:$BD$106&lt;=12)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=12)*(12-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="Q126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;13-$F$11+2,$E$106:$BD$106,"&lt;="&amp;13)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=13-$F$11+2)*($E$106:$BD$106&lt;=13)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=13)*(13-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="R126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;14-$F$11+2,$E$106:$BD$106,"&lt;="&amp;14)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=14-$F$11+2)*($E$106:$BD$106&lt;=14)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=14)*(14-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="S126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;15-$F$11+2,$E$106:$BD$106,"&lt;="&amp;15)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=15-$F$11+2)*($E$106:$BD$106&lt;=15)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=15)*(15-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="T126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;16-$F$11+2,$E$106:$BD$106,"&lt;="&amp;16)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=16-$F$11+2)*($E$106:$BD$106&lt;=16)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=16)*(16-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="U126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;17-$F$11+2,$E$106:$BD$106,"&lt;="&amp;17)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=17-$F$11+2)*($E$106:$BD$106&lt;=17)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=17)*(17-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="V126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;18-$F$11+2,$E$106:$BD$106,"&lt;="&amp;18)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=18-$F$11+2)*($E$106:$BD$106&lt;=18)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=18)*(18-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="W126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;19-$F$11+2,$E$106:$BD$106,"&lt;="&amp;19)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=19-$F$11+2)*($E$106:$BD$106&lt;=19)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=19)*(19-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="X126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;20-$F$11+2,$E$106:$BD$106,"&lt;="&amp;20)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=20-$F$11+2)*($E$106:$BD$106&lt;=20)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=20)*(20-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="Y126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;21-$F$11+2,$E$106:$BD$106,"&lt;="&amp;21)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=21-$F$11+2)*($E$106:$BD$106&lt;=21)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=21)*(21-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="Z126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;22-$F$11+2,$E$106:$BD$106,"&lt;="&amp;22)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=22-$F$11+2)*($E$106:$BD$106&lt;=22)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=22)*(22-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AA126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;23-$F$11+2,$E$106:$BD$106,"&lt;="&amp;23)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=23-$F$11+2)*($E$106:$BD$106&lt;=23)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=23)*(23-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AB126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;24-$F$11+2,$E$106:$BD$106,"&lt;="&amp;24)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=24-$F$11+2)*($E$106:$BD$106&lt;=24)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=24)*(24-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AC126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;25-$F$11+2,$E$106:$BD$106,"&lt;="&amp;25)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=25-$F$11+2)*($E$106:$BD$106&lt;=25)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=25)*(25-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AD126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;26-$F$11+2,$E$106:$BD$106,"&lt;="&amp;26)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=26-$F$11+2)*($E$106:$BD$106&lt;=26)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=26)*(26-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AE126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;27-$F$11+2,$E$106:$BD$106,"&lt;="&amp;27)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=27-$F$11+2)*($E$106:$BD$106&lt;=27)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=27)*(27-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AF126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;28-$F$11+2,$E$106:$BD$106,"&lt;="&amp;28)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=28-$F$11+2)*($E$106:$BD$106&lt;=28)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=28)*(28-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AG126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;29-$F$11+2,$E$106:$BD$106,"&lt;="&amp;29)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=29-$F$11+2)*($E$106:$BD$106&lt;=29)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=29)*(29-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AH126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;30-$F$11+2,$E$106:$BD$106,"&lt;="&amp;30)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=30-$F$11+2)*($E$106:$BD$106&lt;=30)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=30)*(30-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AI126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;31-$F$11+2,$E$106:$BD$106,"&lt;="&amp;31)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=31-$F$11+2)*($E$106:$BD$106&lt;=31)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=31)*(31-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AJ126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;32-$F$11+2,$E$106:$BD$106,"&lt;="&amp;32)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=32-$F$11+2)*($E$106:$BD$106&lt;=32)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=32)*(32-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AK126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;33-$F$11+2,$E$106:$BD$106,"&lt;="&amp;33)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=33-$F$11+2)*($E$106:$BD$106&lt;=33)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=33)*(33-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AL126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;34-$F$11+2,$E$106:$BD$106,"&lt;="&amp;34)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=34-$F$11+2)*($E$106:$BD$106&lt;=34)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=34)*(34-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AM126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;35-$F$11+2,$E$106:$BD$106,"&lt;="&amp;35)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=35-$F$11+2)*($E$106:$BD$106&lt;=35)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=35)*(35-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AN126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;36-$F$11+2,$E$106:$BD$106,"&lt;="&amp;36)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=36-$F$11+2)*($E$106:$BD$106&lt;=36)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=36)*(36-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AO126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;37-$F$11+2,$E$106:$BD$106,"&lt;="&amp;37)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=37-$F$11+2)*($E$106:$BD$106&lt;=37)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=37)*(37-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AP126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;38-$F$11+2,$E$106:$BD$106,"&lt;="&amp;38)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=38-$F$11+2)*($E$106:$BD$106&lt;=38)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=38)*(38-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AQ126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;39-$F$11+2,$E$106:$BD$106,"&lt;="&amp;39)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=39-$F$11+2)*($E$106:$BD$106&lt;=39)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=39)*(39-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AR126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;40-$F$11+2,$E$106:$BD$106,"&lt;="&amp;40)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=40-$F$11+2)*($E$106:$BD$106&lt;=40)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=40)*(40-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AS126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;41-$F$11+2,$E$106:$BD$106,"&lt;="&amp;41)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=41-$F$11+2)*($E$106:$BD$106&lt;=41)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=41)*(41-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AT126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;42-$F$11+2,$E$106:$BD$106,"&lt;="&amp;42)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=42-$F$11+2)*($E$106:$BD$106&lt;=42)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=42)*(42-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AU126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;43-$F$11+2,$E$106:$BD$106,"&lt;="&amp;43)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=43-$F$11+2)*($E$106:$BD$106&lt;=43)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=43)*(43-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AV126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;44-$F$11+2,$E$106:$BD$106,"&lt;="&amp;44)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=44-$F$11+2)*($E$106:$BD$106&lt;=44)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=44)*(44-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AW126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;45-$F$11+2,$E$106:$BD$106,"&lt;="&amp;45)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=45-$F$11+2)*($E$106:$BD$106&lt;=45)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=45)*(45-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AX126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;46-$F$11+2,$E$106:$BD$106,"&lt;="&amp;46)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=46-$F$11+2)*($E$106:$BD$106&lt;=46)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=46)*(46-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AY126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;47-$F$11+2,$E$106:$BD$106,"&lt;="&amp;47)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=47-$F$11+2)*($E$106:$BD$106&lt;=47)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=47)*(47-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="AZ126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;48-$F$11+2,$E$106:$BD$106,"&lt;="&amp;48)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=48-$F$11+2)*($E$106:$BD$106&lt;=48)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=48)*(48-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="BA126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;49-$F$11+2,$E$106:$BD$106,"&lt;="&amp;49)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=49-$F$11+2)*($E$106:$BD$106&lt;=49)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=49)*(49-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="BB126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;50-$F$11+2,$E$106:$BD$106,"&lt;="&amp;50)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=50-$F$11+2)*($E$106:$BD$106&lt;=50)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=50)*(50-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="BC126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;51-$F$11+2,$E$106:$BD$106,"&lt;="&amp;51)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=51-$F$11+2)*($E$106:$BD$106&lt;=51)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=51)*(51-$E$106:$BD$106)))</f>
         <v/>
       </c>
       <c r="BD126" s="34">
-        <f>SUMIFS($E$107:$BD$107,$E$106:$BD$106,"&gt;="&amp;52-$F$11+2,$E$106:$BD$106,"&lt;="&amp;52)</f>
+        <f>SUMPRODUCT(($E$106:$BD$106&gt;=52-$F$11+2)*($E$106:$BD$106&lt;=52)*$E$107:$BD$107*POWER(1-$G$11,($E$106:$BD$106&lt;=52)*(52-$E$106:$BD$106)))</f>
         <v/>
       </c>
     </row>
@@ -17345,211 +17345,211 @@
         </is>
       </c>
       <c r="E153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;1-$F$12+2,$E$131:$BD$131,"&lt;="&amp;1)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=1-$F$12+2)*($E$131:$BD$131&lt;=1)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=1)*(1-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="F153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;2-$F$12+2,$E$131:$BD$131,"&lt;="&amp;2)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=2-$F$12+2)*($E$131:$BD$131&lt;=2)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=2)*(2-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="G153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;3-$F$12+2,$E$131:$BD$131,"&lt;="&amp;3)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=3-$F$12+2)*($E$131:$BD$131&lt;=3)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=3)*(3-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="H153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;4-$F$12+2,$E$131:$BD$131,"&lt;="&amp;4)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=4-$F$12+2)*($E$131:$BD$131&lt;=4)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=4)*(4-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="I153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;5-$F$12+2,$E$131:$BD$131,"&lt;="&amp;5)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=5-$F$12+2)*($E$131:$BD$131&lt;=5)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=5)*(5-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="J153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;6-$F$12+2,$E$131:$BD$131,"&lt;="&amp;6)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=6-$F$12+2)*($E$131:$BD$131&lt;=6)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=6)*(6-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="K153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;7-$F$12+2,$E$131:$BD$131,"&lt;="&amp;7)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=7-$F$12+2)*($E$131:$BD$131&lt;=7)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=7)*(7-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="L153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;8-$F$12+2,$E$131:$BD$131,"&lt;="&amp;8)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=8-$F$12+2)*($E$131:$BD$131&lt;=8)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=8)*(8-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="M153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;9-$F$12+2,$E$131:$BD$131,"&lt;="&amp;9)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=9-$F$12+2)*($E$131:$BD$131&lt;=9)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=9)*(9-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="N153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;10-$F$12+2,$E$131:$BD$131,"&lt;="&amp;10)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=10-$F$12+2)*($E$131:$BD$131&lt;=10)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=10)*(10-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="O153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;11-$F$12+2,$E$131:$BD$131,"&lt;="&amp;11)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=11-$F$12+2)*($E$131:$BD$131&lt;=11)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=11)*(11-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="P153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;12-$F$12+2,$E$131:$BD$131,"&lt;="&amp;12)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=12-$F$12+2)*($E$131:$BD$131&lt;=12)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=12)*(12-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="Q153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;13-$F$12+2,$E$131:$BD$131,"&lt;="&amp;13)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=13-$F$12+2)*($E$131:$BD$131&lt;=13)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=13)*(13-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="R153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;14-$F$12+2,$E$131:$BD$131,"&lt;="&amp;14)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=14-$F$12+2)*($E$131:$BD$131&lt;=14)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=14)*(14-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="S153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;15-$F$12+2,$E$131:$BD$131,"&lt;="&amp;15)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=15-$F$12+2)*($E$131:$BD$131&lt;=15)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=15)*(15-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="T153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;16-$F$12+2,$E$131:$BD$131,"&lt;="&amp;16)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=16-$F$12+2)*($E$131:$BD$131&lt;=16)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=16)*(16-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="U153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;17-$F$12+2,$E$131:$BD$131,"&lt;="&amp;17)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=17-$F$12+2)*($E$131:$BD$131&lt;=17)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=17)*(17-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="V153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;18-$F$12+2,$E$131:$BD$131,"&lt;="&amp;18)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=18-$F$12+2)*($E$131:$BD$131&lt;=18)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=18)*(18-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="W153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;19-$F$12+2,$E$131:$BD$131,"&lt;="&amp;19)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=19-$F$12+2)*($E$131:$BD$131&lt;=19)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=19)*(19-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="X153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;20-$F$12+2,$E$131:$BD$131,"&lt;="&amp;20)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=20-$F$12+2)*($E$131:$BD$131&lt;=20)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=20)*(20-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="Y153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;21-$F$12+2,$E$131:$BD$131,"&lt;="&amp;21)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=21-$F$12+2)*($E$131:$BD$131&lt;=21)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=21)*(21-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="Z153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;22-$F$12+2,$E$131:$BD$131,"&lt;="&amp;22)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=22-$F$12+2)*($E$131:$BD$131&lt;=22)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=22)*(22-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AA153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;23-$F$12+2,$E$131:$BD$131,"&lt;="&amp;23)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=23-$F$12+2)*($E$131:$BD$131&lt;=23)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=23)*(23-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AB153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;24-$F$12+2,$E$131:$BD$131,"&lt;="&amp;24)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=24-$F$12+2)*($E$131:$BD$131&lt;=24)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=24)*(24-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AC153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;25-$F$12+2,$E$131:$BD$131,"&lt;="&amp;25)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=25-$F$12+2)*($E$131:$BD$131&lt;=25)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=25)*(25-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AD153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;26-$F$12+2,$E$131:$BD$131,"&lt;="&amp;26)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=26-$F$12+2)*($E$131:$BD$131&lt;=26)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=26)*(26-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AE153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;27-$F$12+2,$E$131:$BD$131,"&lt;="&amp;27)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=27-$F$12+2)*($E$131:$BD$131&lt;=27)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=27)*(27-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AF153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;28-$F$12+2,$E$131:$BD$131,"&lt;="&amp;28)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=28-$F$12+2)*($E$131:$BD$131&lt;=28)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=28)*(28-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AG153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;29-$F$12+2,$E$131:$BD$131,"&lt;="&amp;29)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=29-$F$12+2)*($E$131:$BD$131&lt;=29)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=29)*(29-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AH153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;30-$F$12+2,$E$131:$BD$131,"&lt;="&amp;30)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=30-$F$12+2)*($E$131:$BD$131&lt;=30)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=30)*(30-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AI153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;31-$F$12+2,$E$131:$BD$131,"&lt;="&amp;31)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=31-$F$12+2)*($E$131:$BD$131&lt;=31)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=31)*(31-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AJ153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;32-$F$12+2,$E$131:$BD$131,"&lt;="&amp;32)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=32-$F$12+2)*($E$131:$BD$131&lt;=32)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=32)*(32-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AK153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;33-$F$12+2,$E$131:$BD$131,"&lt;="&amp;33)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=33-$F$12+2)*($E$131:$BD$131&lt;=33)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=33)*(33-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AL153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;34-$F$12+2,$E$131:$BD$131,"&lt;="&amp;34)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=34-$F$12+2)*($E$131:$BD$131&lt;=34)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=34)*(34-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AM153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;35-$F$12+2,$E$131:$BD$131,"&lt;="&amp;35)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=35-$F$12+2)*($E$131:$BD$131&lt;=35)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=35)*(35-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AN153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;36-$F$12+2,$E$131:$BD$131,"&lt;="&amp;36)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=36-$F$12+2)*($E$131:$BD$131&lt;=36)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=36)*(36-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AO153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;37-$F$12+2,$E$131:$BD$131,"&lt;="&amp;37)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=37-$F$12+2)*($E$131:$BD$131&lt;=37)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=37)*(37-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AP153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;38-$F$12+2,$E$131:$BD$131,"&lt;="&amp;38)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=38-$F$12+2)*($E$131:$BD$131&lt;=38)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=38)*(38-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AQ153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;39-$F$12+2,$E$131:$BD$131,"&lt;="&amp;39)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=39-$F$12+2)*($E$131:$BD$131&lt;=39)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=39)*(39-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AR153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;40-$F$12+2,$E$131:$BD$131,"&lt;="&amp;40)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=40-$F$12+2)*($E$131:$BD$131&lt;=40)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=40)*(40-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AS153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;41-$F$12+2,$E$131:$BD$131,"&lt;="&amp;41)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=41-$F$12+2)*($E$131:$BD$131&lt;=41)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=41)*(41-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AT153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;42-$F$12+2,$E$131:$BD$131,"&lt;="&amp;42)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=42-$F$12+2)*($E$131:$BD$131&lt;=42)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=42)*(42-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AU153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;43-$F$12+2,$E$131:$BD$131,"&lt;="&amp;43)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=43-$F$12+2)*($E$131:$BD$131&lt;=43)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=43)*(43-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AV153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;44-$F$12+2,$E$131:$BD$131,"&lt;="&amp;44)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=44-$F$12+2)*($E$131:$BD$131&lt;=44)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=44)*(44-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AW153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;45-$F$12+2,$E$131:$BD$131,"&lt;="&amp;45)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=45-$F$12+2)*($E$131:$BD$131&lt;=45)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=45)*(45-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AX153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;46-$F$12+2,$E$131:$BD$131,"&lt;="&amp;46)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=46-$F$12+2)*($E$131:$BD$131&lt;=46)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=46)*(46-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AY153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;47-$F$12+2,$E$131:$BD$131,"&lt;="&amp;47)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=47-$F$12+2)*($E$131:$BD$131&lt;=47)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=47)*(47-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="AZ153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;48-$F$12+2,$E$131:$BD$131,"&lt;="&amp;48)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=48-$F$12+2)*($E$131:$BD$131&lt;=48)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=48)*(48-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="BA153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;49-$F$12+2,$E$131:$BD$131,"&lt;="&amp;49)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=49-$F$12+2)*($E$131:$BD$131&lt;=49)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=49)*(49-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="BB153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;50-$F$12+2,$E$131:$BD$131,"&lt;="&amp;50)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=50-$F$12+2)*($E$131:$BD$131&lt;=50)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=50)*(50-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="BC153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;51-$F$12+2,$E$131:$BD$131,"&lt;="&amp;51)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=51-$F$12+2)*($E$131:$BD$131&lt;=51)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=51)*(51-$E$131:$BD$131)))</f>
         <v/>
       </c>
       <c r="BD153" s="34">
-        <f>SUMIFS($E$132:$BD$132,$E$131:$BD$131,"&gt;="&amp;52-$F$12+2,$E$131:$BD$131,"&lt;="&amp;52)</f>
+        <f>SUMPRODUCT(($E$131:$BD$131&gt;=52-$F$12+2)*($E$131:$BD$131&lt;=52)*$E$132:$BD$132*POWER(1-$G$12,($E$131:$BD$131&lt;=52)*(52-$E$131:$BD$131)))</f>
         <v/>
       </c>
     </row>
@@ -21613,211 +21613,211 @@
         </is>
       </c>
       <c r="E178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;1-$F$13+2,$E$158:$BD$158,"&lt;="&amp;1)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=1-$F$13+2)*($E$158:$BD$158&lt;=1)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=1)*(1-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="F178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;2-$F$13+2,$E$158:$BD$158,"&lt;="&amp;2)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=2-$F$13+2)*($E$158:$BD$158&lt;=2)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=2)*(2-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="G178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;3-$F$13+2,$E$158:$BD$158,"&lt;="&amp;3)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=3-$F$13+2)*($E$158:$BD$158&lt;=3)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=3)*(3-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="H178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;4-$F$13+2,$E$158:$BD$158,"&lt;="&amp;4)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=4-$F$13+2)*($E$158:$BD$158&lt;=4)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=4)*(4-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="I178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;5-$F$13+2,$E$158:$BD$158,"&lt;="&amp;5)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=5-$F$13+2)*($E$158:$BD$158&lt;=5)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=5)*(5-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="J178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;6-$F$13+2,$E$158:$BD$158,"&lt;="&amp;6)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=6-$F$13+2)*($E$158:$BD$158&lt;=6)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=6)*(6-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="K178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;7-$F$13+2,$E$158:$BD$158,"&lt;="&amp;7)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=7-$F$13+2)*($E$158:$BD$158&lt;=7)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=7)*(7-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="L178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;8-$F$13+2,$E$158:$BD$158,"&lt;="&amp;8)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=8-$F$13+2)*($E$158:$BD$158&lt;=8)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=8)*(8-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="M178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;9-$F$13+2,$E$158:$BD$158,"&lt;="&amp;9)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=9-$F$13+2)*($E$158:$BD$158&lt;=9)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=9)*(9-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="N178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;10-$F$13+2,$E$158:$BD$158,"&lt;="&amp;10)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=10-$F$13+2)*($E$158:$BD$158&lt;=10)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=10)*(10-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="O178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;11-$F$13+2,$E$158:$BD$158,"&lt;="&amp;11)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=11-$F$13+2)*($E$158:$BD$158&lt;=11)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=11)*(11-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="P178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;12-$F$13+2,$E$158:$BD$158,"&lt;="&amp;12)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=12-$F$13+2)*($E$158:$BD$158&lt;=12)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=12)*(12-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="Q178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;13-$F$13+2,$E$158:$BD$158,"&lt;="&amp;13)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=13-$F$13+2)*($E$158:$BD$158&lt;=13)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=13)*(13-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="R178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;14-$F$13+2,$E$158:$BD$158,"&lt;="&amp;14)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=14-$F$13+2)*($E$158:$BD$158&lt;=14)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=14)*(14-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="S178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;15-$F$13+2,$E$158:$BD$158,"&lt;="&amp;15)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=15-$F$13+2)*($E$158:$BD$158&lt;=15)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=15)*(15-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="T178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;16-$F$13+2,$E$158:$BD$158,"&lt;="&amp;16)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=16-$F$13+2)*($E$158:$BD$158&lt;=16)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=16)*(16-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="U178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;17-$F$13+2,$E$158:$BD$158,"&lt;="&amp;17)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=17-$F$13+2)*($E$158:$BD$158&lt;=17)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=17)*(17-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="V178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;18-$F$13+2,$E$158:$BD$158,"&lt;="&amp;18)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=18-$F$13+2)*($E$158:$BD$158&lt;=18)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=18)*(18-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="W178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;19-$F$13+2,$E$158:$BD$158,"&lt;="&amp;19)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=19-$F$13+2)*($E$158:$BD$158&lt;=19)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=19)*(19-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="X178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;20-$F$13+2,$E$158:$BD$158,"&lt;="&amp;20)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=20-$F$13+2)*($E$158:$BD$158&lt;=20)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=20)*(20-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="Y178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;21-$F$13+2,$E$158:$BD$158,"&lt;="&amp;21)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=21-$F$13+2)*($E$158:$BD$158&lt;=21)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=21)*(21-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="Z178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;22-$F$13+2,$E$158:$BD$158,"&lt;="&amp;22)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=22-$F$13+2)*($E$158:$BD$158&lt;=22)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=22)*(22-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AA178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;23-$F$13+2,$E$158:$BD$158,"&lt;="&amp;23)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=23-$F$13+2)*($E$158:$BD$158&lt;=23)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=23)*(23-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AB178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;24-$F$13+2,$E$158:$BD$158,"&lt;="&amp;24)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=24-$F$13+2)*($E$158:$BD$158&lt;=24)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=24)*(24-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AC178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;25-$F$13+2,$E$158:$BD$158,"&lt;="&amp;25)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=25-$F$13+2)*($E$158:$BD$158&lt;=25)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=25)*(25-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AD178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;26-$F$13+2,$E$158:$BD$158,"&lt;="&amp;26)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=26-$F$13+2)*($E$158:$BD$158&lt;=26)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=26)*(26-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AE178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;27-$F$13+2,$E$158:$BD$158,"&lt;="&amp;27)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=27-$F$13+2)*($E$158:$BD$158&lt;=27)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=27)*(27-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AF178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;28-$F$13+2,$E$158:$BD$158,"&lt;="&amp;28)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=28-$F$13+2)*($E$158:$BD$158&lt;=28)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=28)*(28-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AG178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;29-$F$13+2,$E$158:$BD$158,"&lt;="&amp;29)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=29-$F$13+2)*($E$158:$BD$158&lt;=29)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=29)*(29-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AH178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;30-$F$13+2,$E$158:$BD$158,"&lt;="&amp;30)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=30-$F$13+2)*($E$158:$BD$158&lt;=30)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=30)*(30-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AI178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;31-$F$13+2,$E$158:$BD$158,"&lt;="&amp;31)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=31-$F$13+2)*($E$158:$BD$158&lt;=31)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=31)*(31-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AJ178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;32-$F$13+2,$E$158:$BD$158,"&lt;="&amp;32)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=32-$F$13+2)*($E$158:$BD$158&lt;=32)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=32)*(32-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AK178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;33-$F$13+2,$E$158:$BD$158,"&lt;="&amp;33)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=33-$F$13+2)*($E$158:$BD$158&lt;=33)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=33)*(33-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AL178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;34-$F$13+2,$E$158:$BD$158,"&lt;="&amp;34)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=34-$F$13+2)*($E$158:$BD$158&lt;=34)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=34)*(34-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AM178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;35-$F$13+2,$E$158:$BD$158,"&lt;="&amp;35)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=35-$F$13+2)*($E$158:$BD$158&lt;=35)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=35)*(35-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AN178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;36-$F$13+2,$E$158:$BD$158,"&lt;="&amp;36)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=36-$F$13+2)*($E$158:$BD$158&lt;=36)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=36)*(36-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AO178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;37-$F$13+2,$E$158:$BD$158,"&lt;="&amp;37)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=37-$F$13+2)*($E$158:$BD$158&lt;=37)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=37)*(37-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AP178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;38-$F$13+2,$E$158:$BD$158,"&lt;="&amp;38)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=38-$F$13+2)*($E$158:$BD$158&lt;=38)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=38)*(38-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AQ178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;39-$F$13+2,$E$158:$BD$158,"&lt;="&amp;39)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=39-$F$13+2)*($E$158:$BD$158&lt;=39)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=39)*(39-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AR178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;40-$F$13+2,$E$158:$BD$158,"&lt;="&amp;40)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=40-$F$13+2)*($E$158:$BD$158&lt;=40)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=40)*(40-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AS178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;41-$F$13+2,$E$158:$BD$158,"&lt;="&amp;41)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=41-$F$13+2)*($E$158:$BD$158&lt;=41)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=41)*(41-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AT178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;42-$F$13+2,$E$158:$BD$158,"&lt;="&amp;42)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=42-$F$13+2)*($E$158:$BD$158&lt;=42)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=42)*(42-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AU178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;43-$F$13+2,$E$158:$BD$158,"&lt;="&amp;43)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=43-$F$13+2)*($E$158:$BD$158&lt;=43)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=43)*(43-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AV178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;44-$F$13+2,$E$158:$BD$158,"&lt;="&amp;44)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=44-$F$13+2)*($E$158:$BD$158&lt;=44)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=44)*(44-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AW178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;45-$F$13+2,$E$158:$BD$158,"&lt;="&amp;45)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=45-$F$13+2)*($E$158:$BD$158&lt;=45)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=45)*(45-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AX178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;46-$F$13+2,$E$158:$BD$158,"&lt;="&amp;46)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=46-$F$13+2)*($E$158:$BD$158&lt;=46)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=46)*(46-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AY178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;47-$F$13+2,$E$158:$BD$158,"&lt;="&amp;47)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=47-$F$13+2)*($E$158:$BD$158&lt;=47)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=47)*(47-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="AZ178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;48-$F$13+2,$E$158:$BD$158,"&lt;="&amp;48)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=48-$F$13+2)*($E$158:$BD$158&lt;=48)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=48)*(48-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="BA178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;49-$F$13+2,$E$158:$BD$158,"&lt;="&amp;49)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=49-$F$13+2)*($E$158:$BD$158&lt;=49)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=49)*(49-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="BB178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;50-$F$13+2,$E$158:$BD$158,"&lt;="&amp;50)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=50-$F$13+2)*($E$158:$BD$158&lt;=50)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=50)*(50-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="BC178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;51-$F$13+2,$E$158:$BD$158,"&lt;="&amp;51)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=51-$F$13+2)*($E$158:$BD$158&lt;=51)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=51)*(51-$E$158:$BD$158)))</f>
         <v/>
       </c>
       <c r="BD178" s="34">
-        <f>SUMIFS($E$159:$BD$159,$E$158:$BD$158,"&gt;="&amp;52-$F$13+2,$E$158:$BD$158,"&lt;="&amp;52)</f>
+        <f>SUMPRODUCT(($E$158:$BD$158&gt;=52-$F$13+2)*($E$158:$BD$158&lt;=52)*$E$159:$BD$159*POWER(1-$G$13,($E$158:$BD$158&lt;=52)*(52-$E$158:$BD$158)))</f>
         <v/>
       </c>
     </row>

--- a/toy_models/farm_toy_v5_full_calendar.xlsx
+++ b/toy_models/farm_toy_v5_full_calendar.xlsx
@@ -140,9 +140,9 @@
   <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A136"/>
+  <dimension ref="A1:A139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -588,463 +588,467 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>BUILT 2026-08-30 13:25   (from source at commit a6c69e1)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>If that timestamp is older than the change you are looking for, you have a stale copy —</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>close the file and re-open it from WSL rather than from a recent-files list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
           <t>WHAT v5 ADDS — both of these you spotted missing from v4</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>1. IT CHOOSES WHEN TO PLANT.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t xml:space="preserve">   All 68 plantings the app's calendar generator offers are on the sheet, one row per legal</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">   start week. The solver puts acres on some and zero on others — and zero acres IS the</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   decision not to plant that week. v4 offered five that I picked by hand.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>2. IT CHOOSES WHETHER TO PLANT AT ALL.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">   The BLUE column is a binary per planting, tied to the acres by two constraints that are</t>
+          <t xml:space="preserve">   decision not to plant that week. v4 offered five that I picked by hand.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the app's own C9 and C10:</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        acres &lt;= 'max if planted'   you cannot plant acres without deciding to plant</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2. IT CHOOSES WHETHER TO PLANT AT ALL.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">        acres &gt;= 'min if planted'   if you plant at all, you plant a real block</t>
+          <t xml:space="preserve">   The BLUE column is a binary per planting, tied to the acres by two constraints that are</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">   That is what stops it planting a third of an acre, and it makes this a MILP — which is</t>
+          <t xml:space="preserve">   the app's own C9 and C10:</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   what farm_v2/solver.py is. Its `integrality` array marks the very same y block.</t>
+          <t xml:space="preserve">        acres &lt;= 'max if planted'   you cannot plant acres without deciding to plant</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        acres &gt;= 'min if planted'   if you plant at all, you plant a real block</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>WHAT THE TWO CHANGES ARE WORTH — measured, and they pull OPPOSITE ways</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   That is what stops it planting a third of an acre, and it makes this a MILP — which is</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">     v4, five hand-picked plantings          $1,094,831</t>
+          <t xml:space="preserve">   what farm_v2/solver.py is. Its `integrality` array marks the very same y block.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     v5 without the minimum-acreage rule     $2,387,990   (42 plantings)</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     v5 as it ships                          $2,384,231   (33 plantings)</t>
+          <t>WHAT THE TWO CHANGES ARE WORTH — measured, and they pull OPPOSITE ways</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     v4, five hand-picked plantings          $1,094,831</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t xml:space="preserve">     v5 without the minimum-acreage rule     $2,387,990   (42 plantings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     v5 as it ships                          $2,384,231   (33 plantings)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>Letting it choose the weeks more than doubles profit. Then the minimum-acreage rule takes</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>$3,759 back and drops the plan from 42 plantings to 33, because the</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>slivers are gone.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Neither number means anything alone. A fixed calendar UNDERSTATES; a missing minimum</t>
+          <t>$3,759 back and drops the plan from 42 plantings to 33, because the</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>slivers are gone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Neither number means anything alone. A fixed calendar UNDERSTATES; a missing minimum</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>acreage OVERSTATES. That is why the real model has both, and it is the reason it is a MILP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>rather than a plain LP.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>WHY IT PLANTS SO MANY — this is the finding worth keeping</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33 plantings out of 68, staggered across the season rather than a few big</t>
+          <t>rather than a plain LP.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>blocks. That is SUCCESSION PLANTING, and now you can see why it pays: spreading the harvest</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>is what lets you serve a WEEKLY demand cap continuously. Plant it all at once and one huge</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>WHY IT PLANTS SO MANY — this is the finding worth keeping</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>harvest slams into the ceiling, the cooler fills, and the surplus is wasted or dumped cheap.</t>
+          <t>33 plantings out of 68, staggered across the season rather than a few big</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>blocks. That is SUCCESSION PLANTING, and now you can see why it pays: spreading the harvest</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A model with a fixed planting calendar cannot express the thing the practice exists for.</t>
+          <t>is what lets you serve a WEEKLY demand cap continuously. Plant it all at once and one huge</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>harvest slams into the ceiling, the cooler fills, and the surplus is wasted or dumped cheap.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>!! IT NEEDS LIBREOFFICE, AND THIS ONE IS A REAL MILP</t>
-        </is>
-      </c>
+      <c r="A39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>A model with a fixed planting calendar cannot express the thing the practice exists for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>!! IT NEEDS LIBREOFFICE, AND THIS ONE IS A REAL MILP</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>448 decision cells: 68 acres + 68 binaries + 312 offered. The engine MUST be</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>CoinMP — it does branch and bound over the integers. Expect it to take appreciably longer</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>than v4; integers are what make an optimizer work for its living.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>WHERE THINGS ARE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  YELLOW   you type: the farm, the crop table, the crop x channel table.</t>
+          <t>than v4; integers are what make an optimizer work for its living.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  GREEN    the solver writes: the ACRES column (C28:C95), the six OFFERED rows, and</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">           the PROFIT cell (B200).</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>WHERE THINGS ARE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BLUE     the solver writes: the PLANT? binaries (D28:D95).</t>
+          <t xml:space="preserve">  YELLOW   you type: the farm, the crop table, the crop x channel table.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Everything else is a formula. Columns A-D stay put when you scroll right.</t>
+          <t xml:space="preserve">  GREEN    the solver writes: the ACRES column (C28:C95), the six OFFERED rows, and</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           the PROFIT cell (B200).</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>HOW TO RUN IT</t>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BLUE     the solver writes: the PLANT? binaries (D28:D95).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Section 7 lists every entry with exact ranges. In short:</t>
+          <t xml:space="preserve">  Everything else is a formula. Columns A-D stay put when you scroll right.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Tools &gt; Solver, target the PROFIT cell, set to MAXIMUM</t>
-        </is>
-      </c>
+      <c r="A53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Changing cells: C28:C95 and D28:D95 together, plus the six OFFERED rows</t>
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>HOW TO RUN IT</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Add the constraint  D28:D95 = Binary   — without it the binaries are just numbers</t>
+          <t>Section 7 lists every entry with exact ranges. In short:</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">   and the minimum-acreage rule silently stops working</t>
+          <t xml:space="preserve">   Tools &gt; Solver, target the PROFIT cell, set to MAXIMUM</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t xml:space="preserve">   Changing cells: C28:C95 and D28:D95 together, plus the six OFFERED rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Add the constraint  D28:D95 = Binary   — without it the binaries are just numbers</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   and the minimum-acreage rule silently stops working</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Options: engine = LibreOffice CoinMP Linear Solver; tick non-negative</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>WHAT IT SHOULD FIND</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">     PROFIT   $2,384,231      = revenue $2,558,846 - growing cost $174,616</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">     33 of 68 plantings used</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>Computed by solving the same MILP with scipy.milp — the same HiGHS solver your app runs. A</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>few dollars apart is tolerances. Materially different means one of the two models is not the</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>model we think it is.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>WHAT SELL-THROUGH IS, AND WHY IT SHIPS AT 1.00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Every 'Sell-through' in section 3 is 1.00, matching the app since 30 Aug. The 85% it used to</t>
+          <t>model we think it is.</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>carry had no source, and it was being charged on channels where a purchase order exists and</t>
-        </is>
-      </c>
+      <c r="A69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>nothing goes unsold. So the market-loss and returned-to-store rows all read ZERO right now.</t>
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>WHAT SELL-THROUGH IS, AND WHY IT SHIPS AT 1.00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>That is correct, not broken.</t>
+          <t>Every 'Sell-through' in section 3 is 1.00, matching the app since 30 Aug. The 85% it used to</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>carry had no source, and it was being charged on channels where a purchase order exists and</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>nothing goes unsold. So the market-loss and returned-to-store rows all read ZERO right now.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>That is correct, not broken.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>The narrow definition it now carries:</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     Of what you TAKE TO MARKET, the share that converts to cash — display attrition at a</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     stall, samples, transit damage, a rejected load.</t>
         </is>
       </c>
     </row>
@@ -1052,377 +1056,394 @@
       <c r="A77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Of what you TAKE TO MARKET, the share that converts to cash — display attrition at a</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     stall, samples, transit damage, a rejected load.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>NOT grade-out at harvest (that is pack-out, above the store). NOT spoilage in the store (that</t>
         </is>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>is shrink). And NOT demand uncertainty — which is the one worth understanding, because it is</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>why the old wording could not be right:</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">     The demand ceiling is HARD. At a 6,000 lb cap and 0.85, selling 6,000 means bringing</t>
+          <t>is shrink). And NOT demand uncertainty — which is the one worth understanding, because it is</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">     7,059 and losing 1,059 — every week, including the best Saturday of the year, because</t>
+          <t>why the old wording could not be right:</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     the model will never let you sell 6,001. That is the whole downside of bringing extra</t>
-        </is>
-      </c>
+      <c r="A84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">     with none of the upside. It is not a model of uncertainty; it is a one-sided penalty.</t>
+          <t xml:space="preserve">     The demand ceiling is HARD. At a 6,000 lb cap and 0.85, selling 6,000 means bringing</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     7,059 and losing 1,059 — every week, including the best Saturday of the year, because</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>So what it CAN mean is a display requirement: a picked-over stall sells less than a full one,</t>
+          <t xml:space="preserve">     the model will never let you sell 6,001. That is the whole downside of bringing extra</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>so moving 6,000 lb needs more than 6,000 lb on the table. Deterministic, and an input</t>
+          <t xml:space="preserve">     with none of the upside. It is not a model of uncertainty; it is a one-sided penalty.</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>requirement like seed. Real demand variance is a different problem (newsvendor) needing</t>
-        </is>
-      </c>
+      <c r="A89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>So what it CAN mean is a display requirement: a picked-over stall sells less than a full one,</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>so moving 6,000 lb needs more than 6,000 lb on the table. Deterministic, and an input</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>requirement like seed. Real demand variance is a different problem (newsvendor) needing</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>machinery neither this sheet nor the app has yet.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>THREE THINGS TO TRY</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-    </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 1 — switch sell-through on, and watch the crop decide what happens.</t>
-        </is>
-      </c>
+      <c r="A94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
+          <t>THREE THINGS TO TRY</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 1 — switch sell-through on, and watch the crop decide what happens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">   In section 3 set Spinach / {CH1} sell-through to 0.85, and Garlic / {CH1} to 0.85 too.</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   Re-solve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Both now offer more than they sell. But look at the two 'market loss' rows: Spinach's is</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   positive and Garlic's is ZERO, because garlic's 'Returns to store' is 1.00 — unsold garlic</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   comes home and sells later, so the loss is a DELAY, not a loss.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">   That is the grower's ruling in two cells: the same sell-through means different things on</t>
+          <t xml:space="preserve">   Both now offer more than they sell. But look at the two 'market loss' rows: Spinach's is</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">   different crops, which is why it belongs on the crop x channel row and not on either one</t>
+          <t xml:space="preserve">   positive and Garlic's is ZERO, because garlic's 'Returns to store' is 1.00 — unsold garlic</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">   alone. Now set Garlic's 'Returns to store' to 0.00 and re-solve: the delay becomes a loss</t>
+          <t xml:space="preserve">   comes home and sells later, so the loss is a DELAY, not a loss.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t xml:space="preserve">   That is the grower's ruling in two cells: the same sell-through means different things on</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   different crops, which is why it belongs on the crop x channel row and not on either one</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   alone. Now set Garlic's 'Returns to store' to 0.00 and re-solve: the delay becomes a loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t xml:space="preserve">   and the plan changes.</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>EXPERIMENT 2 — drop the minimum acreage.  Set every 'Min acres if planted' in the crop</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">   table to 0 and re-solve.</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t xml:space="preserve">   Expect $2,387,990 and 42 plantings. The extra profit is real but the plan is</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t xml:space="preserve">   not: it plants fractions of an acre no one would drive a tractor out for. This is what</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   the binaries are FOR, and it is why the app carries them.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="3" t="inlineStr">
-        <is>
-          <t>EXPERIMENT 3 — take away the cooler.  Set the cold store to 40 m3 and re-solve.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t xml:space="preserve">   the binaries are FOR, and it is why the app carries them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>EXPERIMENT 3 — take away the cooler.  Set the cold store to 40 m3 and re-solve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t xml:space="preserve">   Watch WHICH WEEKS it abandons, not just which crop. With a full calendar it can retreat</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t xml:space="preserve">   to a planting pattern that keeps the cooler under its ceiling — an answer v4 could not</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   even represent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>WHAT v5 STILL DOES NOT CARRY</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY: no labour, water, packaging, storage, overhead.</t>
+          <t xml:space="preserve">   even represent.</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    Profit is therefore far too high. The cash layer is next.</t>
-        </is>
-      </c>
+      <c r="A118" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>WHAT v5 STILL DOES NOT CARRY</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Shelf life IS enforced now (a real constraint since you found it dead). Shrink is wired</t>
+          <t xml:space="preserve">  - Costs are seed/transplant per acre ONLY: no labour, water, packaging, storage, overhead.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">    too, but defaults to 0%, so it stays invisible until you set it.</t>
+          <t xml:space="preserve">    Profit is therefore far too high. The cash layer is next.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - No water, labour, diversity or throughput limits.</t>
+          <t xml:space="preserve">  - No cash-flow constraint, so it can spend money it does not have.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Three crops, not seven.</t>
+          <t xml:space="preserve">  - Shelf life IS enforced now (a real constraint since you found it dead). Shrink is wired</t>
         </is>
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    too, but defaults to 0%, so it stays invisible until you set it.</t>
+        </is>
+      </c>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>!! THE SCALE WARNING</t>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - No water, labour, diversity or throughput limits.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t xml:space="preserve">  - Three crops, not seven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>!! THE SCALE WARNING</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>An optimizer's answer is far more scale-sensitive than a calculator's: which constraint binds,</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>and therefore which crop and which WEEK wins, can invert between 3 crops and 7. This teaches</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>the machinery. It is not advice about your farm.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>HAS THIS SHEET BEEN CHECKED?</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yes. Crop data, the calendar and the demand caps are read from the app. The formulas are</t>
+          <t>the machinery. It is not advice about your farm.</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>calculated by an engine and compared cell by cell against an independent model under three</t>
-        </is>
-      </c>
+      <c r="A132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>configurations. Every input is perturbed to prove it propagates. No number is frozen. And the</t>
+      <c r="A133" s="3" t="inlineStr">
+        <is>
+          <t>HAS THIS SHEET BEEN CHECKED?</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>same MILP is solved with scipy.milp, its answer written into the decision cells, and the</t>
+          <t>Yes. Crop data, the calendar and the demand caps are read from the app. The formulas are</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>sheet's own PROFIT cell must reproduce the optimum exactly.</t>
+          <t>calculated by an engine and compared cell by cell against an independent model under three</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
+        <is>
+          <t>configurations. Every input is perturbed to prove it propagates. No number is frozen. And the</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>same MILP is solved with scipy.milp, its answer written into the decision cells, and the</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>sheet's own PROFIT cell must reproduce the optimum exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
         <is>
           <t xml:space="preserve">     Run it yourself:   .venv/bin/python toy_models/verify_toy_v5.py</t>
         </is>
@@ -1509,23 +1530,28 @@
           <t>FARM TOY MODEL — v5: the full calendar (a MILP)</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>BUILT 2026-08-30 13:25   (from source at a6c69e1)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>YELLOW = you type.  GREEN = the solver writes.  BLUE = the solver's plant/don't-plant switches.  Read the 'READ ME' sheet first.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1 — THE FARM</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Land you have</t>
         </is>
@@ -1533,14 +1559,14 @@
       <c r="B5" s="5" t="n">
         <v>80</v>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>acres</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Cold store (cooler)</t>
         </is>
@@ -1548,14 +1574,14 @@
       <c r="B6" s="6" t="n">
         <v>275</v>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>m3 — Spinach, Kale</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Ambient store (barn)</t>
         </is>
@@ -1563,14 +1589,14 @@
       <c r="B7" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>m3 — Garlic</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>2 — HOW EACH CROP BEHAVES</t>
         </is>
@@ -1723,14 +1749,14 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>'Min acres if planted' is what the plant/don't-plant switch enforces — see section 4.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>3 — WHO BUYS IT   (one row per crop x channel — the grower's ruling)</t>
         </is>
@@ -1994,14 +2020,14 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>4 — THE PLANTING CALENDAR   (68 possible plantings — the solver picks)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>One row per legal start week, exactly what the app's generator offers. ACRES and PLANT? are both decisions.</t>
         </is>
@@ -8131,7 +8157,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>ACRES &lt;= 'max if planted' and ACRES &gt;= 'min if planted' are the app's C9 and C10: you cannot plant acres without deciding to plant, and if you plant at all you plant a real block.</t>
         </is>
@@ -8306,12 +8332,12 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>LAND in the ground</t>
         </is>
       </c>
-      <c r="B99" s="4" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>used</t>
         </is>
@@ -8526,7 +8552,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr"/>
+      <c r="A100" s="4" t="inlineStr"/>
       <c r="E100" s="32" t="inlineStr">
         <is>
           <t>&lt;=</t>
@@ -8789,12 +8815,12 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  limit</t>
         </is>
       </c>
-      <c r="B101" s="4" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>cap</t>
         </is>
@@ -9224,14 +9250,14 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="4" t="inlineStr">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Acres standing that week, summed across every planting the solver chose.</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>SPINACH  —  cold store</t>
         </is>
@@ -9403,12 +9429,12 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>Packed out -&gt; INTO the store</t>
         </is>
       </c>
-      <c r="B107" s="4" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -9628,7 +9654,7 @@
           <t>Stock carried in</t>
         </is>
       </c>
-      <c r="B108" s="4" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -9847,7 +9873,7 @@
           <t xml:space="preserve">   lost to shrink</t>
         </is>
       </c>
-      <c r="B109" s="4" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -10062,12 +10088,12 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>In store this week</t>
         </is>
       </c>
-      <c r="B110" s="4" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -10287,7 +10313,7 @@
           <t>Farmers Market — most you may sell this week</t>
         </is>
       </c>
-      <c r="B111" s="4" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -10507,7 +10533,7 @@
           <t>Farmers Market — OFFERED</t>
         </is>
       </c>
-      <c r="B112" s="4" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>lb  &lt;-- SOLVER</t>
         </is>
@@ -10675,7 +10701,7 @@
           <t>Farmers Market — SOLD</t>
         </is>
       </c>
-      <c r="B113" s="4" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -10895,7 +10921,7 @@
           <t xml:space="preserve">   market loss (gone)</t>
         </is>
       </c>
-      <c r="B114" s="4" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -11115,7 +11141,7 @@
           <t xml:space="preserve">   returned to store</t>
         </is>
       </c>
-      <c r="B115" s="4" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -11335,7 +11361,7 @@
           <t xml:space="preserve">   leaves the store (offered - returned)</t>
         </is>
       </c>
-      <c r="B116" s="4" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -11555,7 +11581,7 @@
           <t>Wholesale — most you may sell this week</t>
         </is>
       </c>
-      <c r="B117" s="4" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -11775,7 +11801,7 @@
           <t>Wholesale — OFFERED</t>
         </is>
       </c>
-      <c r="B118" s="4" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>lb  &lt;-- SOLVER</t>
         </is>
@@ -11943,7 +11969,7 @@
           <t>Wholesale — SOLD</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -12163,7 +12189,7 @@
           <t xml:space="preserve">   market loss (gone)</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -12383,7 +12409,7 @@
           <t xml:space="preserve">   returned to store</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -12603,7 +12629,7 @@
           <t xml:space="preserve">   leaves the store (offered - returned)</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -12818,12 +12844,12 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>Stock carried out</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -13038,14 +13064,14 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="4" t="inlineStr">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   ^ subtracts what LEAVES, not what was offered — so 'returned to store' is</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     never taken out at all, and shows up as next week's carried in.</t>
         </is>
@@ -13057,7 +13083,7 @@
           <t>Most stock its shelf life allows</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -13272,19 +13298,19 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Stock carried out must stay at or below this row.</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>ROOM OCCUPANCY</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
@@ -13499,7 +13525,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>KALE  —  cold store</t>
         </is>
@@ -13671,12 +13697,12 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>Packed out -&gt; INTO the store</t>
         </is>
       </c>
-      <c r="B132" s="4" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -13896,7 +13922,7 @@
           <t>Stock carried in</t>
         </is>
       </c>
-      <c r="B133" s="4" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -14115,7 +14141,7 @@
           <t xml:space="preserve">   lost to shrink</t>
         </is>
       </c>
-      <c r="B134" s="4" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -14330,12 +14356,12 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>In store this week</t>
         </is>
       </c>
-      <c r="B135" s="4" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -14555,7 +14581,7 @@
           <t>Farmers Market — most you may sell this week</t>
         </is>
       </c>
-      <c r="B136" s="4" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -14775,7 +14801,7 @@
           <t>Farmers Market — OFFERED</t>
         </is>
       </c>
-      <c r="B137" s="4" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>lb  &lt;-- SOLVER</t>
         </is>
@@ -14943,7 +14969,7 @@
           <t>Farmers Market — SOLD</t>
         </is>
       </c>
-      <c r="B138" s="4" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -15163,7 +15189,7 @@
           <t xml:space="preserve">   market loss (gone)</t>
         </is>
       </c>
-      <c r="B139" s="4" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -15383,7 +15409,7 @@
           <t xml:space="preserve">   returned to store</t>
         </is>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -15603,7 +15629,7 @@
           <t xml:space="preserve">   leaves the store (offered - returned)</t>
         </is>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -15823,7 +15849,7 @@
           <t>Wholesale — most you may sell this week</t>
         </is>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -16038,14 +16064,14 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="4" t="inlineStr">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   ^ Wholesale is an ANNUAL cap (500,000 lb a year), so there is NO weekly limit —</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     this row is what is LEFT of the year, and it falls as you sell.</t>
         </is>
@@ -16057,7 +16083,7 @@
           <t>Wholesale — OFFERED</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>lb  &lt;-- SOLVER</t>
         </is>
@@ -16225,7 +16251,7 @@
           <t>Wholesale — SOLD</t>
         </is>
       </c>
-      <c r="B146" s="4" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -16445,7 +16471,7 @@
           <t xml:space="preserve">   market loss (gone)</t>
         </is>
       </c>
-      <c r="B147" s="4" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -16665,7 +16691,7 @@
           <t xml:space="preserve">   returned to store</t>
         </is>
       </c>
-      <c r="B148" s="4" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -16885,7 +16911,7 @@
           <t xml:space="preserve">   leaves the store (offered - returned)</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -17100,12 +17126,12 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>Stock carried out</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -17320,14 +17346,14 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="4" t="inlineStr">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   ^ subtracts what LEAVES, not what was offered — so 'returned to store' is</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     never taken out at all, and shows up as next week's carried in.</t>
         </is>
@@ -17339,7 +17365,7 @@
           <t>Most stock its shelf life allows</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -17554,19 +17580,19 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="4" t="inlineStr">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Stock carried out must stay at or below this row.</t>
         </is>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>ROOM OCCUPANCY</t>
         </is>
       </c>
-      <c r="B155" s="4" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
@@ -17781,7 +17807,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>GARLIC  —  ambient store</t>
         </is>
@@ -17953,12 +17979,12 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
+      <c r="A159" s="4" t="inlineStr">
         <is>
           <t>Packed out -&gt; INTO the store</t>
         </is>
       </c>
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -18178,7 +18204,7 @@
           <t>Stock carried in</t>
         </is>
       </c>
-      <c r="B160" s="4" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -18397,7 +18423,7 @@
           <t xml:space="preserve">   lost to shrink</t>
         </is>
       </c>
-      <c r="B161" s="4" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -18612,12 +18638,12 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>In store this week</t>
         </is>
       </c>
-      <c r="B162" s="4" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -18837,7 +18863,7 @@
           <t>Farmers Market — most you may sell this week</t>
         </is>
       </c>
-      <c r="B163" s="4" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -19057,7 +19083,7 @@
           <t>Farmers Market — OFFERED</t>
         </is>
       </c>
-      <c r="B164" s="4" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
         <is>
           <t>lb  &lt;-- SOLVER</t>
         </is>
@@ -19225,7 +19251,7 @@
           <t>Farmers Market — SOLD</t>
         </is>
       </c>
-      <c r="B165" s="4" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -19445,7 +19471,7 @@
           <t xml:space="preserve">   market loss (gone)</t>
         </is>
       </c>
-      <c r="B166" s="4" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -19665,7 +19691,7 @@
           <t xml:space="preserve">   returned to store</t>
         </is>
       </c>
-      <c r="B167" s="4" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -19885,7 +19911,7 @@
           <t xml:space="preserve">   leaves the store (offered - returned)</t>
         </is>
       </c>
-      <c r="B168" s="4" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -20105,7 +20131,7 @@
           <t>Wholesale — most you may sell this week</t>
         </is>
       </c>
-      <c r="B169" s="4" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -20325,7 +20351,7 @@
           <t>Wholesale — OFFERED</t>
         </is>
       </c>
-      <c r="B170" s="4" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>lb  &lt;-- SOLVER</t>
         </is>
@@ -20493,7 +20519,7 @@
           <t>Wholesale — SOLD</t>
         </is>
       </c>
-      <c r="B171" s="4" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -20713,7 +20739,7 @@
           <t xml:space="preserve">   market loss (gone)</t>
         </is>
       </c>
-      <c r="B172" s="4" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -20933,7 +20959,7 @@
           <t xml:space="preserve">   returned to store</t>
         </is>
       </c>
-      <c r="B173" s="4" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -21153,7 +21179,7 @@
           <t xml:space="preserve">   leaves the store (offered - returned)</t>
         </is>
       </c>
-      <c r="B174" s="4" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -21368,12 +21394,12 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="inlineStr">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>Stock carried out</t>
         </is>
       </c>
-      <c r="B175" s="4" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -21588,14 +21614,14 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   ^ subtracts what LEAVES, not what was offered — so 'returned to store' is</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">     never taken out at all, and shows up as next week's carried in.</t>
         </is>
@@ -21607,7 +21633,7 @@
           <t>Most stock its shelf life allows</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
         <is>
           <t>lb</t>
         </is>
@@ -21822,19 +21848,19 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="4" t="inlineStr">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Stock carried out must stay at or below this row.</t>
         </is>
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr">
+      <c r="A180" s="4" t="inlineStr">
         <is>
           <t>ROOM OCCUPANCY</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
@@ -22049,7 +22075,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>6 — THE TWO STORES</t>
         </is>
@@ -22229,7 +22255,7 @@
           <t>COLD STORE</t>
         </is>
       </c>
-      <c r="B184" s="4" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
         <is>
           <t>used</t>
         </is>
@@ -22444,7 +22470,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="inlineStr"/>
+      <c r="A185" s="4" t="inlineStr"/>
       <c r="E185" s="32" t="inlineStr">
         <is>
           <t>&lt;=</t>
@@ -22707,12 +22733,12 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="inlineStr">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  limit</t>
         </is>
       </c>
-      <c r="B186" s="4" t="inlineStr">
+      <c r="B186" s="2" t="inlineStr">
         <is>
           <t>cap</t>
         </is>
@@ -23142,7 +23168,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="4" t="inlineStr">
+      <c r="A188" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Holds Spinach, Kale.</t>
         </is>
@@ -23322,7 +23348,7 @@
           <t>AMBIENT STORE</t>
         </is>
       </c>
-      <c r="B191" s="4" t="inlineStr">
+      <c r="B191" s="2" t="inlineStr">
         <is>
           <t>used</t>
         </is>
@@ -23537,7 +23563,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr"/>
+      <c r="A192" s="4" t="inlineStr"/>
       <c r="E192" s="32" t="inlineStr">
         <is>
           <t>&lt;=</t>
@@ -23800,12 +23826,12 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="inlineStr">
+      <c r="A193" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">  limit</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>cap</t>
         </is>
@@ -24235,21 +24261,21 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">   Holds Garlic.</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t>7 — THE OPTIMIZER</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="inlineStr">
+      <c r="A198" s="4" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
@@ -24260,7 +24286,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="inlineStr">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>Growing cost</t>
         </is>
@@ -24269,7 +24295,7 @@
         <f>SUMPRODUCT($C$28:$C$95,($B$28:$B$95="Spinach")*$H$11+($B$28:$B$95="Kale")*$H$12+($B$28:$B$95="Garlic")*$H$13)</f>
         <v/>
       </c>
-      <c r="C199" s="4" t="inlineStr">
+      <c r="C199" s="2" t="inlineStr">
         <is>
           <t>acres x $/acre, across every planting</t>
         </is>
@@ -24285,14 +24311,14 @@
         <f>B198-B199</f>
         <v/>
       </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="C200" s="4" t="inlineStr">
         <is>
           <t>&lt;-- MAXIMISE THIS CELL</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="inlineStr">
+      <c r="A201" s="4" t="inlineStr">
         <is>
           <t>Plantings chosen</t>
         </is>
@@ -24301,14 +24327,14 @@
         <f>SUM($D$28:$D$95)</f>
         <v/>
       </c>
-      <c r="C201" s="4" t="inlineStr">
+      <c r="C201" s="2" t="inlineStr">
         <is>
           <t>of 68 offered</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="inlineStr">
+      <c r="A203" s="4" t="inlineStr">
         <is>
           <t>Annual caps</t>
         </is>
@@ -24335,14 +24361,14 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+      <c r="A206" s="3" t="inlineStr">
         <is>
           <t>SOLVER SETUP — Tools &gt; Solver</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="inlineStr">
+      <c r="A207" s="4" t="inlineStr">
         <is>
           <t>Target cell</t>
         </is>
@@ -24352,14 +24378,14 @@
           <t>$B$200</t>
         </is>
       </c>
-      <c r="G207" s="4" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr">
         <is>
           <t>set to MAXIMUM</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="inlineStr">
+      <c r="A208" s="4" t="inlineStr">
         <is>
           <t>By changing cells</t>
         </is>
@@ -24369,7 +24395,7 @@
           <t>$C$28:$D$95</t>
         </is>
       </c>
-      <c r="G208" s="4" t="inlineStr">
+      <c r="G208" s="2" t="inlineStr">
         <is>
           <t>acres AND plant? together</t>
         </is>
@@ -24386,7 +24412,7 @@
           <t>$E$112:$BD$112;$E$118:$BD$118;$E$137:$BD$137;$E$145:$BD$145;$E$164:$BD$164;$E$170:$BD$170</t>
         </is>
       </c>
-      <c r="G209" s="4" t="inlineStr">
+      <c r="G209" s="2" t="inlineStr">
         <is>
           <t>the OFFERED rows</t>
         </is>
@@ -24415,7 +24441,7 @@
           <t>$C$28:$C$95  &lt;=  $BE$28:$BE$95</t>
         </is>
       </c>
-      <c r="G211" s="4" t="inlineStr">
+      <c r="G211" s="2" t="inlineStr">
         <is>
           <t>no acres without deciding to plant</t>
         </is>
@@ -24432,7 +24458,7 @@
           <t>$C$28:$C$95  &gt;=  $BF$28:$BF$95</t>
         </is>
       </c>
-      <c r="G212" s="4" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>planted means a real block</t>
         </is>
@@ -24557,7 +24583,7 @@
           <t>$E$123:$BD$123  &lt;=  $E$126:$BD$126</t>
         </is>
       </c>
-      <c r="G222" s="4" t="inlineStr">
+      <c r="G222" s="2" t="inlineStr">
         <is>
           <t>nothing held longer than it keeps</t>
         </is>
@@ -24574,7 +24600,7 @@
           <t>$E$150:$BD$150  &lt;=  $E$153:$BD$153</t>
         </is>
       </c>
-      <c r="G223" s="4" t="inlineStr">
+      <c r="G223" s="2" t="inlineStr">
         <is>
           <t>nothing held longer than it keeps</t>
         </is>
@@ -24591,7 +24617,7 @@
           <t>$E$175:$BD$175  &lt;=  $E$178:$BD$178</t>
         </is>
       </c>
-      <c r="G224" s="4" t="inlineStr">
+      <c r="G224" s="2" t="inlineStr">
         <is>
           <t>nothing held longer than it keeps</t>
         </is>
@@ -24634,7 +24660,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="inlineStr">
+      <c r="A228" s="4" t="inlineStr">
         <is>
           <t>Options</t>
         </is>
@@ -24644,7 +24670,7 @@
           <t>engine = LibreOffice CoinMP Linear Solver</t>
         </is>
       </c>
-      <c r="G228" s="4" t="inlineStr">
+      <c r="G228" s="2" t="inlineStr">
         <is>
           <t>tick 'Assume variables as non-negative'</t>
         </is>
